--- a/tests/realSuite/Piano-Viaggi-_Sci-Alpino-Selected-IC-e-IS_27-gen-26-Def_con-vettore/input.xlsx
+++ b/tests/realSuite/Piano-Viaggi-_Sci-Alpino-Selected-IC-e-IS_27-gen-26-Def_con-vettore/input.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C29"/>
+  <dimension ref="A1:C42"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -436,177 +436,177 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>IC ALTA VAL DI SOLE</t>
+          <t>ENAIP CLES</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Via S. Michele,11, Fucine di Ossana (TN)</t>
+          <t>Piazza Fiera, Cles</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>IC BASSA TUENNO</t>
+          <t>ENAIP VILLAZZANO</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Via Maistrelli, 10 - Tuenno</t>
+          <t>Fermata bus, Park ex Italcementi, Trento</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>IC BRENTONICO</t>
+          <t>IC ALTA VAL DI SOLE</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>SSPG - Via F. Calzolari, 2, Brentonico</t>
+          <t>Via S. Michele,11, Fucine di Ossana (TN)</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>IC CHIESE</t>
+          <t>IC BASSA TUENNO</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>SSPG - Via Papaleoni, 5 – Storo</t>
+          <t>Via Maistrelli, 10 - Tuenno</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>IC CHIESE</t>
+          <t>IC BRENTONICO</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>SSPG - Via alla Fiera, 1 - Pieve di Bono</t>
+          <t>SSPG - Via F. Calzolari, 2, Brentonico</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>IC FONDO-REVO’</t>
+          <t>IC CHIESE</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Fermata bus – Vigili del Fuoco – Revò</t>
+          <t>SSPG - Via Papaleoni, 5 – Storo</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>IC FONDO-REVO’</t>
+          <t>IC CHIESE</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Via Pia Laviosa Zambotti 24 - Fondo</t>
+          <t>SSPG - Via alla Fiera, 1 - Pieve di Bono</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>IC GIUDICARIE ESTERIORI</t>
+          <t>IC DAME INGLESI ROVERETO</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Via S. Giovanni Bosco, 14, Comano Terme</t>
+          <t>Parcheggio - Stadio Quercia, Rovereto</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>IC ISERA ROVERETO</t>
+          <t>IC FONDO-REVO’</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Parcheggio - Stadio Quercia, Rovereto</t>
+          <t>Fermata bus – Vigili del Fuoco – Revò</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>IC LADINO DI FASSA</t>
+          <t>IC FONDO-REVO’</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Fermata bus “Hotel Trentino”, Moena</t>
+          <t>Via Pia Laviosa Zambotti 24 - Fondo</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>IC LADINO DI FASSA</t>
+          <t>IC GIUDICARIE ESTERIORI</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Strada Dolomites, Pozza di Fassa 67, Sen Jan/San Giovanni</t>
+          <t>Via S. Giovanni Bosco, 14, Comano Terme</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>IC LAVIS</t>
+          <t>IC ISERA ROVERETO</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>SSPG Via Carlo Sette, 13/A, Lavis (TN)</t>
+          <t>Parcheggio - Stadio Quercia, Rovereto</t>
         </is>
       </c>
       <c r="C13" t="n">
@@ -616,87 +616,87 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>IC MEZZOLOMBARDO PAGANELLA</t>
+          <t>IC LADINO DI FASSA</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Stazione FTM, Mezzolombardo</t>
+          <t>Fermata bus “Hotel Trentino”, Moena</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>IC PERGINE 1</t>
+          <t>IC LADINO DI FASSA</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Piazza Gavazzi, Pergine</t>
+          <t>Strada Dolomites, Pozza di Fassa 67, Sen Jan/San Giovanni</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>IC PRIMIERO</t>
+          <t>IC LAVIS</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Pizzeria Fenadora (vicino alla rotonda di Fonzaso)</t>
+          <t>SSPG Via Carlo Sette, 13/A, Lavis (TN)</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>IC PRIMIERO / IS PRIMIERO</t>
+          <t>IC MEZZOLOMBARDO PAGANELLA</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Stazione autocorriere - Primiero</t>
+          <t>Stazione FTM, Mezzolombardo</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>16</v>
+        <v>9</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>IC TIONE</t>
+          <t>IC PERGINE 1</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Stazione autocorriere, Tione</t>
+          <t>Piazza Gavazzi, Pergine</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>IC TRENTO 2</t>
+          <t>IC PERGINE 2</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Fermata bus, Park ex Italcementi, Trento</t>
+          <t>Piazza Gavazzi, Pergine</t>
         </is>
       </c>
       <c r="C19" t="n">
@@ -706,150 +706,345 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>IC VAL RENDENA</t>
+          <t>IC PRIMIERO</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Fermata Bus - Piazza Palù, Madonna di Campiglio</t>
+          <t>Pizzeria Fenadora (vicino alla rotonda di Fonzaso)</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>IC VAL RENDENA</t>
+          <t>IC PRIMIERO / IS PRIMIERO</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>SP – Frazione Fisto, 108, Spiazzo (TN)</t>
+          <t>Stazione autocorriere - Primiero</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>3</v>
+        <v>16</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>IC VAL RENDENA</t>
+          <t>IC TIONE</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>SSPG – Via Collini Borciol 18, Pinzolo</t>
+          <t>Stazione autocorriere, Tione</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>IC VILLA LAGARINA</t>
+          <t>IC TRENTO 2</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>SSPG - Via Stockstadt am Rhein, 3, Villa Lagarina</t>
+          <t>Fermata bus, Park ex Italcementi, Trento</t>
         </is>
       </c>
       <c r="C23" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>IS BORGO VALSUGANA</t>
+          <t>IC VAL RENDENA</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Stazione Intermodale - Borgo Valsugana</t>
+          <t>Fermata Bus - Piazza Palù, Madonna di Campiglio</t>
         </is>
       </c>
       <c r="C24" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>IS CLES PILATI</t>
+          <t>IC VAL RENDENA</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Piazza Fiera, Cles</t>
+          <t>SP – Frazione Fisto, 108, Spiazzo (TN)</t>
         </is>
       </c>
       <c r="C25" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>IS ROSA BIANCA</t>
+          <t>IC VAL RENDENA</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Corso Degasperi, Predazzo</t>
+          <t>SSPG – Via Collini Borciol 18, Pinzolo</t>
         </is>
       </c>
       <c r="C26" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>IS ROSA BIANCA</t>
+          <t>IC VILLA LAGARINA</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Piazza della Stazione, Cavalese</t>
+          <t>SSPG - Via Stockstadt am Rhein, 3, Villa Lagarina</t>
         </is>
       </c>
       <c r="C27" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>IS ROSMINI ROVERETO Squadra + Students Staff</t>
+          <t>IS BORGO VALSUGANA</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Parcheggio - Stadio Quercia, Rovereto</t>
+          <t>Stazione Intermodale - Borgo Valsugana</t>
         </is>
       </c>
       <c r="C28" t="n">
-        <v>31</v>
+        <v>10</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
+          <t>IS CLES PILATI</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>Piazza Fiera, Cles</t>
+        </is>
+      </c>
+      <c r="C29" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>IS CLES RUSSEL</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>Piazza Fiera, Cles</t>
+        </is>
+      </c>
+      <c r="C30" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>IS DA VINCI TRENTO</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Fermata bus, Park ex Italcementi, Trento</t>
+        </is>
+      </c>
+      <c r="C31" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>IS ENAIP TIONE</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>Stazione autocorriere, Tione</t>
+        </is>
+      </c>
+      <c r="C32" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>IS FILZI ROVERETO</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>Parcheggio - Stadio Quercia, Rovereto</t>
+        </is>
+      </c>
+      <c r="C33" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>IS FONTANA ROVERETO</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>Parcheggio - Stadio Quercia, Rovereto</t>
+        </is>
+      </c>
+      <c r="C34" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>IS GUETTI TIONE</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>Stazione autocorriere, Tione</t>
+        </is>
+      </c>
+      <c r="C35" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>IS MARCONI ROVERETO</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>Parcheggio - Stadio Quercia, Rovereto</t>
+        </is>
+      </c>
+      <c r="C36" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>IS MARTINI MEZZOLOMBARDO</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>Stazione FTM, Mezzolombardo</t>
+        </is>
+      </c>
+      <c r="C37" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>IS PRATI TRENTO</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>Fermata bus, Park ex Italcementi, Trento</t>
+        </is>
+      </c>
+      <c r="C38" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>IS ROSA BIANCA</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>Corso Degasperi, Predazzo</t>
+        </is>
+      </c>
+      <c r="C39" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>IS ROSA BIANCA</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>Piazza della Stazione, Cavalese</t>
+        </is>
+      </c>
+      <c r="C40" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>IS ROSMINI ROVERETO Squadra + Students Staff</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>Parcheggio - Stadio Quercia, Rovereto</t>
+        </is>
+      </c>
+      <c r="C41" t="n">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
           <t>IS TRENTO PERTINI</t>
         </is>
       </c>
-      <c r="B29" t="inlineStr">
+      <c r="B42" t="inlineStr">
         <is>
           <t>Fermata bus, Park ex Italcementi, Trento</t>
         </is>
       </c>
-      <c r="C29" t="n">
+      <c r="C42" t="n">
         <v>9</v>
       </c>
     </row>
